--- a/excel-data/user.xlsx
+++ b/excel-data/user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918E1161-EDCB-46CF-9B63-544E5DAE5A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0E278F-28F4-4525-9CDF-8042F76D3D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1164" yWindow="2988" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant" sheetId="1" r:id="rId1"/>
@@ -647,7 +647,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>18</v>
@@ -676,7 +676,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>18</v>
@@ -705,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>18</v>

--- a/excel-data/user.xlsx
+++ b/excel-data/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0E278F-28F4-4525-9CDF-8042F76D3D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036D95B1-5740-4DB7-BD92-CD78244D1184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
@@ -580,16 +580,16 @@
         <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>14</v>
@@ -609,16 +609,16 @@
         <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>2</v>
@@ -637,17 +637,17 @@
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>18</v>
@@ -666,17 +666,17 @@
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>18</v>
@@ -695,17 +695,17 @@
       <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>18</v>

--- a/excel-data/user.xlsx
+++ b/excel-data/user.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036D95B1-5740-4DB7-BD92-CD78244D1184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A72F7CA-D77B-44F1-B211-3A1C35AC5911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
-    <sheet name="restaurant" sheetId="1" r:id="rId1"/>
+    <sheet name="user" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/excel-data/user.xlsx
+++ b/excel-data/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A72F7CA-D77B-44F1-B211-3A1C35AC5911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EBBAF7-3556-485A-9D38-A48AE3194159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>group_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>super@test.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>$2a$10$FUJ8U5tUUcso8KXDFqcNSufkPq/XeHah8N9mUmyJMLKiODmQOZbaS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,10 +100,6 @@
   </si>
   <si>
     <t>GroupAdmin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Super</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -562,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="22.77734375" style="1" customWidth="1"/>
@@ -577,7 +569,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
@@ -606,7 +598,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -641,19 +633,19 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -670,50 +662,22 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="I4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="5" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -753,7 +717,6 @@
     <row r="42" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="43" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="44" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
